--- a/rules/CORE-000719/negative/01/data/unit-test-coreid-FB0908-negative.xlsx
+++ b/rules/CORE-000719/negative/01/data/unit-test-coreid-FB0908-negative.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Validation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ae.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Library" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ae.xpt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cm.xpt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="mh.xpt" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,6 +565,30 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>Adverse Events</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cm.xpt</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Concomitant/Prior Medications</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mh.xpt</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Medical History</t>
         </is>
       </c>
     </row>
@@ -577,7 +603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,6 +636,324 @@
         <is>
           <t>Error value</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Headaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>10019231</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Headaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10019232</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Headaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Headaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>10019231</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>10057166</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AEHLGT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vascular hypertensive disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ae.xpt</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AEHLGTCD</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>10057166</v>
       </c>
     </row>
   </sheetData>
@@ -2717,4 +3061,5354 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>CMSEQ</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>CMTRT</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>CMINDC</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>CMDOSE</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>CMDOSU</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>CMDOSFRQ</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>CMROUTE</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>EPOCH</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>CMSTDTC</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>CMENDTC</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>CMSTDY</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>CMENDY</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>CMENRTPT</t>
+        </is>
+      </c>
+      <c r="Q1" s="5" t="inlineStr">
+        <is>
+          <t>CMENTPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Reported Name of Drug, Med, or Therapy</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Indication</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Dose per Administration</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Dose Units</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Dosing Frequency per Interval</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>Route of Administration</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>Epoch</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>Start Date/Time of Medication</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>End Date/Time of Medication</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>Study Day of Start of Medication</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>Study Day of End of Medication</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>End Relative to Reference Time Point</t>
+        </is>
+      </c>
+      <c r="Q2" s="7" t="inlineStr">
+        <is>
+          <t>End Reference Time Point</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q4" s="7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>QD</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-29</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>METAMUCIL</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>PRN</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>2012-08</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q6" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>HYDROCORTISONE, TOPICAL</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>TOPICAL</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-11</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>HYTRIN</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>Q4H</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-19</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="O8" s="9" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>QID</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-29</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>FEOSOL</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>325</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>Q6H</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-29</t>
+        </is>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>PRAVACHOL</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-08</t>
+        </is>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>160</v>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>DEMEROL</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>INTRAVENOUS</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>2012-11-21</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
+        <is>
+          <t>2012-11-21</t>
+        </is>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>TYLENOL W/CODEINE NO. 3</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>2012-11-21</t>
+        </is>
+      </c>
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>2012-11-21</t>
+        </is>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>HYDROCORTISONE</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>TOPICAL</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>2012-12-08</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-14</t>
+        </is>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>LOMOTIL</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-04</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-04</t>
+        </is>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="O15" s="9" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>MYLANTA</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-05</t>
+        </is>
+      </c>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-14</t>
+        </is>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>52</v>
+      </c>
+      <c r="O16" s="9" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>ADVIL</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q17" s="9" t="inlineStr">
+        <is>
+          <t>2014-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>MULTIVITAMINS</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>2014-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>EXCEDRIN</t>
+        </is>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>2014-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>METAMUCIL</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>2012-03-01</t>
+        </is>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>-546</v>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>2014-02-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>NEO-SYNEPHRINE</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>NASAL</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-01</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-30</t>
+        </is>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="O21" s="9" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>PSEUDOEPHEDRINE HYDROCHLORIDE</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-02</t>
+        </is>
+      </c>
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-30</t>
+        </is>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" s="9" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>CDISC004</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>VITAMIN C</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="P23" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q23" s="9" t="inlineStr">
+        <is>
+          <t>2014-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>CDISC004</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>VITAMIN E</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="P24" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q24" s="9" t="inlineStr">
+        <is>
+          <t>2014-03-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>CDISC005</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>CENTRUM SILVER</t>
+        </is>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L25" s="9" t="inlineStr">
+        <is>
+          <t>2012-03</t>
+        </is>
+      </c>
+      <c r="P25" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q25" s="9" t="inlineStr">
+        <is>
+          <t>2013-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>CDISC005</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>CEPHALEXIN</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>2013-07-19</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>2013-08-01</t>
+        </is>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>CDISC005</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>PROMETHAZINE HCL W/CODEINE</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr">
+        <is>
+          <t>2013-07-19</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>2013-07-25</t>
+        </is>
+      </c>
+      <c r="N27" s="9" t="n">
+        <v>166</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>CDISC005</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>HYDROCORTISONE</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>TOPICAL</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-14</t>
+        </is>
+      </c>
+      <c r="N28" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="P28" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q28" s="9" t="inlineStr">
+        <is>
+          <t>2013-08-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>CDISC007</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>METAMUCIL</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="P29" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q29" s="9" t="inlineStr">
+        <is>
+          <t>2013-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>CDISC007</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>ADVIL</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="P30" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q30" s="9" t="inlineStr">
+        <is>
+          <t>2013-06-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>CDISC007</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>DOCUSATE SODIUM</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K31" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr">
+        <is>
+          <t>2012-11</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-05</t>
+        </is>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>CDISC007</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>BENADRYL</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr">
+        <is>
+          <t>2013-02-18</t>
+        </is>
+      </c>
+      <c r="M32" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-10</t>
+        </is>
+      </c>
+      <c r="N32" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>CDISC007</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>PREDNISONE</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L33" s="9" t="inlineStr">
+        <is>
+          <t>2013-02-18</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-10</t>
+        </is>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>CDISC007</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>TEMOVATE</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>TOPICAL</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>2013-02-18</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="inlineStr">
+        <is>
+          <t>2013-02-20</t>
+        </is>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>ATROVENT</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>RESPIRATORY (INHALATION)</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L35" s="9" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="inlineStr">
+        <is>
+          <t>2014-10-31</t>
+        </is>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>VENTOLIN</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>RESPIRATORY (INHALATION)</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
+        <is>
+          <t>2014-10-31</t>
+        </is>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>CARDURA</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L37" s="9" t="inlineStr">
+        <is>
+          <t>2012-09</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="inlineStr">
+        <is>
+          <t>2014-10-31</t>
+        </is>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>AEROBID</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>RESPIRATORY (INHALATION)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L38" s="9" t="inlineStr">
+        <is>
+          <t>2013-09</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="inlineStr">
+        <is>
+          <t>2014-10-31</t>
+        </is>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>CDISC008</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>VITAMIN E</t>
+        </is>
+      </c>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>2014-01</t>
+        </is>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
+        <is>
+          <t>2014-10-31</t>
+        </is>
+      </c>
+      <c r="O39" s="9" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>CDISC009</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>TYLENOL</t>
+        </is>
+      </c>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>325</v>
+      </c>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L40" s="9" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="P40" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q40" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>CDISC009</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E41" s="9" t="inlineStr">
+        <is>
+          <t>NORVASC</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H41" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>2010-07</t>
+        </is>
+      </c>
+      <c r="P41" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q41" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>CDISC009</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>LORAZEPAM</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>PRIMARY STUDY CONDITION</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L42" s="9" t="inlineStr">
+        <is>
+          <t>2012-11-20</t>
+        </is>
+      </c>
+      <c r="M42" s="9" t="inlineStr">
+        <is>
+          <t>2012-11-24</t>
+        </is>
+      </c>
+      <c r="N42" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="O42" s="9" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>CDISC010</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>MECLIZINE</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L43" s="9" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="M43" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-08</t>
+        </is>
+      </c>
+      <c r="O43" s="9" t="n">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>CDISC010</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>CAPOTEN</t>
+        </is>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>CDISC010</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>POTASSIUM</t>
+        </is>
+      </c>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K45" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L45" s="9" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="P45" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q45" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>CDISC010</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>PRILOSEC</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L46" s="9" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="P46" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q46" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>CDISC010</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E47" s="9" t="inlineStr">
+        <is>
+          <t>PROPULSID</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G47" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L47" s="9" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="P47" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q47" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>CDISC010</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E48" s="9" t="inlineStr">
+        <is>
+          <t>LANOXIN</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L48" s="9" t="inlineStr">
+        <is>
+          <t>2011-06</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q48" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>CDISC010</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>ZESTORETIC</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K49" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L49" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-15</t>
+        </is>
+      </c>
+      <c r="N49" s="9" t="n">
+        <v>-6</v>
+      </c>
+      <c r="P49" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q49" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>CDISC011</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>MOTRIN</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L50" s="9" t="inlineStr">
+        <is>
+          <t>1998-10</t>
+        </is>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="O50" s="9" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>CDISC011</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>PRINIVIL</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H51" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K51" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L51" s="9" t="inlineStr">
+        <is>
+          <t>2011-07-15</t>
+        </is>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="N51" s="9" t="n">
+        <v>-511</v>
+      </c>
+      <c r="O51" s="9" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>CDISC011</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" s="9" t="inlineStr">
+        <is>
+          <t>HYDROCORTISONE, TOPICAL</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>TRANSDERMAL</t>
+        </is>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L52" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-10</t>
+        </is>
+      </c>
+      <c r="M52" s="9" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="N52" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="O52" s="9" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>CDISC011</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>CALAMINE LOTION</t>
+        </is>
+      </c>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr">
+        <is>
+          <t>ng</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>TRANSDERMAL</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L53" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-23</t>
+        </is>
+      </c>
+      <c r="M53" s="9" t="inlineStr">
+        <is>
+          <t>2013-06-05</t>
+        </is>
+      </c>
+      <c r="N53" s="9" t="n">
+        <v>138</v>
+      </c>
+      <c r="O53" s="9" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>CDISC014</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>ASPIRIN</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="n">
+        <v>325</v>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L54" s="9" t="inlineStr">
+        <is>
+          <t>2012-07</t>
+        </is>
+      </c>
+      <c r="P54" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q54" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>CDISC014</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>DYAZIDE</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G55" s="9" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L55" s="9" t="inlineStr">
+        <is>
+          <t>2013-03-02</t>
+        </is>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>-32</v>
+      </c>
+      <c r="P55" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q55" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>CDISC014</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>TYLENOL</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>325</v>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K56" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L56" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-01</t>
+        </is>
+      </c>
+      <c r="M56" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-15</t>
+        </is>
+      </c>
+      <c r="N56" s="9" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O56" s="9" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C57" s="9" t="inlineStr">
+        <is>
+          <t>CDISC014</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>AMOXICILLIN</t>
+        </is>
+      </c>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G57" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="H57" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K57" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L57" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
+      </c>
+      <c r="N57" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="P57" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q57" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>CDISC014</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>BENZONATATE</t>
+        </is>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="H58" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L58" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-01</t>
+        </is>
+      </c>
+      <c r="N58" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="P58" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q58" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>CDISC016</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>PREMARIN</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L59" s="9" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="P59" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q59" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>CDISC016</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>SYNTHROID</t>
+        </is>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H60" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K60" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>2009-03-03</t>
+        </is>
+      </c>
+      <c r="M60" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-20</t>
+        </is>
+      </c>
+      <c r="N60" s="9" t="n">
+        <v>-1492</v>
+      </c>
+      <c r="O60" s="9" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C61" s="9" t="inlineStr">
+        <is>
+          <t>CDISC016</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" s="9" t="inlineStr">
+        <is>
+          <t>ROBITUSSIN</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K61" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L61" s="9" t="inlineStr">
+        <is>
+          <t>2013-04-28</t>
+        </is>
+      </c>
+      <c r="M61" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-04</t>
+        </is>
+      </c>
+      <c r="N61" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="O61" s="9" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>CDISC016</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" s="9" t="inlineStr">
+        <is>
+          <t>ARMOUR THYROID</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>2013-05-21</t>
+        </is>
+      </c>
+      <c r="N62" s="9" t="n">
+        <v>49</v>
+      </c>
+      <c r="P62" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q62" s="9" t="inlineStr">
+        <is>
+          <t>2013-09-22</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>CDISC017</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="9" t="inlineStr">
+        <is>
+          <t>ACETAMINOPHEN</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K63" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="P63" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q63" s="9" t="inlineStr">
+        <is>
+          <t>2014-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>CDISC017</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>MULTIVITAMIN</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="P64" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q64" s="9" t="inlineStr">
+        <is>
+          <t>2014-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>CDISC017</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>VITAMIN E</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H65" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>2011-08</t>
+        </is>
+      </c>
+      <c r="P65" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q65" s="9" t="inlineStr">
+        <is>
+          <t>2014-03-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>CDISC017</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>CALAMINE LOTION</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>TOPICAL</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L66" s="9" t="inlineStr">
+        <is>
+          <t>2013-12-29</t>
+        </is>
+      </c>
+      <c r="M66" s="9" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="N66" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="O66" s="9" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>CDISC017</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>CORTISONE</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>TOPICAL</t>
+        </is>
+      </c>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L67" s="9" t="inlineStr">
+        <is>
+          <t>2013-12-29</t>
+        </is>
+      </c>
+      <c r="M67" s="9" t="inlineStr">
+        <is>
+          <t>2014-02-01</t>
+        </is>
+      </c>
+      <c r="N67" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="O67" s="9" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>CDISC018</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>MULTIVITAMINS</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K68" s="9" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="L68" s="9" t="inlineStr">
+        <is>
+          <t>2002-08</t>
+        </is>
+      </c>
+      <c r="P68" s="9" t="inlineStr">
+        <is>
+          <t>ONGOING</t>
+        </is>
+      </c>
+      <c r="Q68" s="9" t="inlineStr">
+        <is>
+          <t>2013-06-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>CDISC018</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>ADVIL</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G69" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="H69" s="9" t="inlineStr">
+        <is>
+          <t>mg</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K69" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>2012-12-30</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>2012-12-30</t>
+        </is>
+      </c>
+      <c r="N69" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="O69" s="9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>CDISC018</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>MYLANTA</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K70" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-16</t>
+        </is>
+      </c>
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-16</t>
+        </is>
+      </c>
+      <c r="N70" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="O70" s="9" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>CDISC018</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>MYLANTA</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>TABLET</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L71" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-21</t>
+        </is>
+      </c>
+      <c r="M71" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-24</t>
+        </is>
+      </c>
+      <c r="N71" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="O71" s="9" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>CDISC018</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>CALAMINE LOTION</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>PROPHYLAXIS OR NON-THERAPEUTIC USE</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="inlineStr">
+        <is>
+          <t>TOPICAL</t>
+        </is>
+      </c>
+      <c r="K72" s="9" t="inlineStr">
+        <is>
+          <t>TREATMENT</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-27</t>
+        </is>
+      </c>
+      <c r="M72" s="9" t="inlineStr">
+        <is>
+          <t>2013-01-27</t>
+        </is>
+      </c>
+      <c r="N72" s="9" t="n">
+        <v>42</v>
+      </c>
+      <c r="O72" s="9" t="n">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>STUDYID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>DOMAIN</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>USUBJID</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>MHSEQ</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>MHTERM</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>MHLLT</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>MHLLTCD</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>MHDECOD</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>MHPTCD</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>MHHLT</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>MHHLTCD</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>MHBODSYS</t>
+        </is>
+      </c>
+      <c r="M1" s="5" t="inlineStr">
+        <is>
+          <t>MHBDSYCD</t>
+        </is>
+      </c>
+      <c r="N1" s="5" t="inlineStr">
+        <is>
+          <t>MHEVDTYP</t>
+        </is>
+      </c>
+      <c r="O1" s="5" t="inlineStr">
+        <is>
+          <t>MHSTDTC</t>
+        </is>
+      </c>
+      <c r="P1" s="5" t="inlineStr">
+        <is>
+          <t>MHSTDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>Study Identifier</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Domain Abbreviation</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>Unique Subject Identifier</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>Sequence Number</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>Reported Term for the Medical History</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>Lowest Level Term</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>Lowest Level Term Code</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>Dictionary-Derived Term</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>Preferred Term Code</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>High Level Term</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>High Level Term Code</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="inlineStr">
+        <is>
+          <t>Body System or Organ Class</t>
+        </is>
+      </c>
+      <c r="M2" s="7" t="inlineStr">
+        <is>
+          <t>Body System or Organ Class Code</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>Medical History Event Date Type</t>
+        </is>
+      </c>
+      <c r="O2" s="7" t="inlineStr">
+        <is>
+          <t>Start Date/Time of Medical History Event</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>Study Day of Start of Observation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="O3" s="7" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="P3" s="7" t="inlineStr">
+        <is>
+          <t>Num</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>19</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>65</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="O4" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="P4" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>CDISC001</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>ALZHEIMER'S DISEASE</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>10001896</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>Dementia Alzheimer's type</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>10012271</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease (incl subtypes)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>10001897</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>Nervous system disorders</t>
+        </is>
+      </c>
+      <c r="M5" s="9" t="inlineStr">
+        <is>
+          <t>10029205</t>
+        </is>
+      </c>
+      <c r="N5" s="9" t="inlineStr">
+        <is>
+          <t>SYMPTOM ONSET</t>
+        </is>
+      </c>
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>2004-05-28</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>-3108</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>CDISC002</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>ALZHEIMER'S DISEASE</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>10001896</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Dementia Alzheimer's type</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>10012271</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease (incl subtypes)</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>10001898</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>Nervous system disorders</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>10029205</t>
+        </is>
+      </c>
+      <c r="N6" s="9" t="inlineStr">
+        <is>
+          <t>SYMPTOM ONSET</t>
+        </is>
+      </c>
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>2010-03-19</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>-972</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>CDISC003</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>ALZHEIMER'S DISEASE</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>10001896</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Dementia Alzheimer's type</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>10012271</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease (incl subtypes)</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="n"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>Nervous system disorders</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>10029205</t>
+        </is>
+      </c>
+      <c r="N7" s="9" t="inlineStr">
+        <is>
+          <t>SYMPTOM ONSET</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>2007-02-09</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>-2393</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>CDISC004</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>ALZHEIMER'S DISEASE</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>10001896</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>Dementia Alzheimer's type</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>10012271</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease (incl subtype)</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>10001897</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>Nervous system disorders</t>
+        </is>
+      </c>
+      <c r="M8" s="9" t="inlineStr">
+        <is>
+          <t>10029205</t>
+        </is>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>SYMPTOM ONSET</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>2010-11-05</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>-1068</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>MH</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>CDISC005</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>ALZHEIMER'S DISEASE</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>10001896</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>Dementia Alzheimer's type</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>10012271</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>Alzheimer's disease (incl subtype)</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>10001898</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>Nervous system disorders</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
+        <is>
+          <t>10029205</t>
+        </is>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>SYMPTOM ONSET</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>2006-08-20</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>-2360</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>